--- a/ENTREGA_FINAL/RESULTADOS_ATUAIS/Modelo_A_Baseline_Oficial/08_Avaliacao_Liquida_do_Governo_por_Sexo.xlsx
+++ b/ENTREGA_FINAL/RESULTADOS_ATUAIS/Modelo_A_Baseline_Oficial/08_Avaliacao_Liquida_do_Governo_por_Sexo.xlsx
@@ -14,7 +14,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodologia" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mulheres_15d'!$A$1:$E$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mulheres_30d'!$A$1:$E$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Homens_15d'!$A$1:$E$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Homens_30d'!$A$1:$E$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cobertura'!$A$1:$H$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Metodologia'!$A$1:$B$6</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -25,7 +32,7 @@
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,16 +43,25 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -59,17 +75,29 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,307 +465,315 @@
   </sheetPr>
   <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>avaliacao_liquida_suavizada</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>ic_baixo</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>ic_alto</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>se_pp</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>45684</v>
       </c>
       <c r="B2" t="n">
         <v>-13</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="5" t="n">
         <v>-20.29412124019156</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="5" t="n">
         <v>-5.705878759808441</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="5" t="n">
         <v>3.721558813185679</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="4" t="n">
         <v>45727</v>
       </c>
       <c r="B3" t="n">
         <v>-7</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="5" t="n">
         <v>-11.05731472051303</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="5" t="n">
         <v>-2.942685279486968</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="5" t="n">
         <v>2.070096569384241</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>45733</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="5" t="n">
         <v>-10.64564261575694</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="5" t="n">
         <v>-14.41521997793285</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="5" t="n">
         <v>-6.876065253581032</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="5" t="n">
         <v>1.92328909710069</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="4" t="n">
         <v>45810</v>
       </c>
       <c r="B5" t="n">
         <v>-20</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="5" t="n">
         <v>-27.15677657486863</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="5" t="n">
         <v>-12.84322342513137</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="5" t="n">
         <v>3.651483716701108</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="4" t="n">
         <v>45817</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="5" t="n">
         <v>-14.0494745666212</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="5" t="n">
         <v>-17.66040321758339</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="5" t="n">
         <v>-10.43854591565901</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="5" t="n">
         <v>1.842344389715698</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="4" t="n">
         <v>45865</v>
       </c>
       <c r="B7" t="n">
         <v>-16</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="5" t="n">
         <v>-23.14782500591836</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="5" t="n">
         <v>-8.852174994081636</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="5" t="n">
         <v>3.646916505762094</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="4" t="n">
         <v>45908</v>
       </c>
       <c r="B8" t="n">
         <v>-3</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="5" t="n">
         <v>-7.066461068279784</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="5" t="n">
         <v>1.066461068279784</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="5" t="n">
         <v>2.07476315909655</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="4" t="n">
         <v>45929</v>
       </c>
       <c r="B9" t="n">
         <v>-15</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="5" t="n">
         <v>-22.33613236507662</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="5" t="n">
         <v>-7.663867634923379</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="5" t="n">
         <v>3.74299345444258</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="4" t="n">
         <v>45999</v>
       </c>
       <c r="B10" t="n">
         <v>-5</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="5" t="n">
         <v>-9.066739921067569</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="5" t="n">
         <v>-0.9332600789324319</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="5" t="n">
         <v>2.074905433541378</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="4" t="n">
         <v>46006</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="5" t="n">
         <v>-10.77225806599006</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="5" t="n">
         <v>-14.58638890453079</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="5" t="n">
         <v>-6.958127227449324</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="5" t="n">
         <v>1.946020880294797</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="4" t="n">
         <v>46048</v>
       </c>
       <c r="B12" t="n">
         <v>-18</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="5" t="n">
         <v>-25.32477814424173</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="5" t="n">
         <v>-10.67522185575827</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="5" t="n">
         <v>3.737200378179723</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="4" t="n">
         <v>46090</v>
       </c>
       <c r="B13" t="n">
         <v>-4</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="5" t="n">
         <v>-8.097923834482193</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="5" t="n">
         <v>0.09792383448219333</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="5" t="n">
         <v>2.090815885805093</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="4" t="n">
         <v>46104</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="5" t="n">
         <v>-17.52098363377991</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="5" t="n">
         <v>-21.95971475527867</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="5" t="n">
         <v>-13.08225251228114</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="5" t="n">
         <v>2.26470034985893</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="4" t="n">
         <v>46190</v>
       </c>
       <c r="B15" t="n">
         <v>-4</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="5" t="n">
         <v>-8.060101106255477</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="5" t="n">
         <v>0.06010110625547593</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="5" t="n">
         <v>2.071518220886218</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="4" t="n">
         <v>46197</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="5" t="n">
         <v>-3.588395998576696</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="5" t="n">
         <v>-7.607425343700053</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="5" t="n">
         <v>0.4306333465466601</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="5" t="n">
         <v>2.050562855657016</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="4" t="n">
         <v>46203</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="5" t="n">
         <v>-6.068160523531096</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="5" t="n">
         <v>-10.10276623387245</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="5" t="n">
         <v>-2.033554813189745</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="5" t="n">
         <v>2.058510126801209</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -750,307 +786,315 @@
   </sheetPr>
   <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>avaliacao_liquida_suavizada</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>ic_baixo</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>ic_alto</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>se_pp</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>45684</v>
       </c>
       <c r="B2" t="n">
         <v>-13</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="5" t="n">
         <v>-20.29412124019156</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="5" t="n">
         <v>-5.705878759808441</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="5" t="n">
         <v>3.721558813185679</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="4" t="n">
         <v>45727</v>
       </c>
       <c r="B3" t="n">
         <v>-7</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="5" t="n">
         <v>-11.05731472051303</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="5" t="n">
         <v>-2.942685279486968</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="5" t="n">
         <v>2.070096569384241</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>45733</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="5" t="n">
         <v>-10.49077847018357</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="5" t="n">
         <v>-14.21294563827658</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="5" t="n">
         <v>-6.76861130209056</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="5" t="n">
         <v>1.899099778084185</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="4" t="n">
         <v>45810</v>
       </c>
       <c r="B5" t="n">
         <v>-20</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="5" t="n">
         <v>-27.15677657486863</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="5" t="n">
         <v>-12.84322342513137</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="5" t="n">
         <v>3.651483716701108</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="4" t="n">
         <v>45817</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="5" t="n">
         <v>-14.23498420560668</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="5" t="n">
         <v>-17.88691848562913</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="5" t="n">
         <v>-10.58304992558422</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="5" t="n">
         <v>1.863266013471907</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="4" t="n">
         <v>45865</v>
       </c>
       <c r="B7" t="n">
         <v>-16</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="5" t="n">
         <v>-23.14782500591836</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="5" t="n">
         <v>-8.852174994081636</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="5" t="n">
         <v>3.646916505762094</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="4" t="n">
         <v>45908</v>
       </c>
       <c r="B8" t="n">
         <v>-3</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="5" t="n">
         <v>-7.066461068279784</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="5" t="n">
         <v>1.066461068279784</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="5" t="n">
         <v>2.07476315909655</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="4" t="n">
         <v>45929</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="5" t="n">
         <v>-8.369067355409236</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="5" t="n">
         <v>-12.34687896760045</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="5" t="n">
         <v>-4.391255743218022</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="5" t="n">
         <v>2.02953301365111</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="4" t="n">
         <v>45999</v>
       </c>
       <c r="B10" t="n">
         <v>-5</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="5" t="n">
         <v>-9.066739921067569</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="5" t="n">
         <v>-0.9332600789324319</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="5" t="n">
         <v>2.074905433541378</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="4" t="n">
         <v>46006</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="5" t="n">
         <v>-10.46712112089293</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="5" t="n">
         <v>-14.21808000858869</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="5" t="n">
         <v>-6.716162233197176</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="5" t="n">
         <v>1.913789700873507</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="4" t="n">
         <v>46048</v>
       </c>
       <c r="B12" t="n">
         <v>-18</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="5" t="n">
         <v>-25.32477814424173</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="5" t="n">
         <v>-10.67522185575827</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="5" t="n">
         <v>3.737200378179723</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="4" t="n">
         <v>46090</v>
       </c>
       <c r="B13" t="n">
         <v>-4</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="5" t="n">
         <v>-8.097923834482193</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="5" t="n">
         <v>0.09792383448219333</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="5" t="n">
         <v>2.090815885805093</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="4" t="n">
         <v>46104</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="5" t="n">
         <v>-14.29736756679915</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="5" t="n">
         <v>-18.19380446873339</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="5" t="n">
         <v>-10.40093066486491</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="5" t="n">
         <v>1.988014541424655</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="4" t="n">
         <v>46190</v>
       </c>
       <c r="B15" t="n">
         <v>-4</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="5" t="n">
         <v>-8.060101106255477</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="5" t="n">
         <v>0.06010110625547593</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="5" t="n">
         <v>2.071518220886218</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="4" t="n">
         <v>46197</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="5" t="n">
         <v>-3.610179032997621</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="5" t="n">
         <v>-7.548025481519772</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="5" t="n">
         <v>0.3276674155245294</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="5" t="n">
         <v>2.009142249338958</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="4" t="n">
         <v>46203</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="5" t="n">
         <v>-5.760478989739919</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="5" t="n">
         <v>-9.498440710313407</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="5" t="n">
         <v>-2.022517269166431</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="5" t="n">
         <v>1.907158371305827</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1063,307 +1107,315 @@
   </sheetPr>
   <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>avaliacao_liquida_suavizada</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>ic_baixo</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>ic_alto</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>se_pp</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>45684</v>
       </c>
       <c r="B2" t="n">
         <v>-20</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="5" t="n">
         <v>-27.40994274002537</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="5" t="n">
         <v>-12.59005725997463</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="5" t="n">
         <v>3.780652501002087</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="4" t="n">
         <v>45727</v>
       </c>
       <c r="B3" t="n">
         <v>-21</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="5" t="n">
         <v>-25.16344625022034</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="5" t="n">
         <v>-16.83655374977966</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="5" t="n">
         <v>2.124246304044907</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>45733</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="5" t="n">
         <v>-21.81835263018868</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="5" t="n">
         <v>-25.69595895139545</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="5" t="n">
         <v>-17.94074630898191</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="5" t="n">
         <v>1.978406925735796</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="4" t="n">
         <v>45810</v>
       </c>
       <c r="B5" t="n">
         <v>-27</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="5" t="n">
         <v>-34.29412124019156</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="5" t="n">
         <v>-19.70587875980844</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="5" t="n">
         <v>3.721558813185679</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="4" t="n">
         <v>45817</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="5" t="n">
         <v>-25.68462526058833</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="5" t="n">
         <v>-29.36584458568689</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="5" t="n">
         <v>-22.00340593548976</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="5" t="n">
         <v>1.87820763755638</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="4" t="n">
         <v>45865</v>
       </c>
       <c r="B7" t="n">
         <v>-24</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="5" t="n">
         <v>-31.33351372056518</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="5" t="n">
         <v>-16.66648627943482</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="5" t="n">
         <v>3.741657386773942</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="4" t="n">
         <v>45908</v>
       </c>
       <c r="B8" t="n">
         <v>-12</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="5" t="n">
         <v>-16.2198942956584</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="5" t="n">
         <v>-7.780105704341597</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="5" t="n">
         <v>2.153046856444501</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="4" t="n">
         <v>45929</v>
       </c>
       <c r="B9" t="n">
         <v>-24</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="5" t="n">
         <v>-31.38744373781133</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="5" t="n">
         <v>-16.61255626218867</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="5" t="n">
         <v>3.769173207305107</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="4" t="n">
         <v>45999</v>
       </c>
       <c r="B10" t="n">
         <v>-13</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="5" t="n">
         <v>-17.22352685929889</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="5" t="n">
         <v>-8.776473140701114</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="5" t="n">
         <v>2.154900239297011</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="4" t="n">
         <v>46006</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="5" t="n">
         <v>-18.41044128223237</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="5" t="n">
         <v>-22.31997292738307</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="5" t="n">
         <v>-14.50090963708166</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="5" t="n">
         <v>1.99469565562867</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="4" t="n">
         <v>46048</v>
       </c>
       <c r="B12" t="n">
         <v>-27</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="5" t="n">
         <v>-34.34659760914891</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="5" t="n">
         <v>-19.65340239085109</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="5" t="n">
         <v>3.748332962798263</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="4" t="n">
         <v>46090</v>
       </c>
       <c r="B13" t="n">
         <v>-10</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="5" t="n">
         <v>-14.31690540079501</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="5" t="n">
         <v>-5.68309459920499</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="5" t="n">
         <v>2.202543227756331</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="4" t="n">
         <v>46104</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="5" t="n">
         <v>-16.00248295847918</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="5" t="n">
         <v>-20.59177569478133</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="5" t="n">
         <v>-11.41319022217704</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="5" t="n">
         <v>2.341518911827921</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="4" t="n">
         <v>46190</v>
       </c>
       <c r="B15" t="n">
         <v>-9</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="5" t="n">
         <v>-13.27070168398211</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="5" t="n">
         <v>-4.729298316017893</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="5" t="n">
         <v>2.178969469678452</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="4" t="n">
         <v>46197</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="5" t="n">
         <v>-14.83724005409968</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="5" t="n">
         <v>-18.88941560145413</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="5" t="n">
         <v>-10.78506450674523</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="5" t="n">
         <v>2.067474494081265</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="4" t="n">
         <v>46203</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="5" t="n">
         <v>-12.2015890842227</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="5" t="n">
         <v>-16.25412051078606</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="5" t="n">
         <v>-8.149057657659336</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="5" t="n">
         <v>2.067656068442693</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1376,307 +1428,315 @@
   </sheetPr>
   <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>avaliacao_liquida_suavizada</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>ic_baixo</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>ic_alto</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>se_pp</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>45684</v>
       </c>
       <c r="B2" t="n">
         <v>-20</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="5" t="n">
         <v>-27.40994274002537</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="5" t="n">
         <v>-12.59005725997463</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="5" t="n">
         <v>3.780652501002087</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="4" t="n">
         <v>45727</v>
       </c>
       <c r="B3" t="n">
         <v>-21</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="5" t="n">
         <v>-25.16344625022034</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="5" t="n">
         <v>-16.83655374977966</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="5" t="n">
         <v>2.124246304044907</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>45733</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="5" t="n">
         <v>-21.78381936589648</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="5" t="n">
         <v>-25.61166099798422</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="5" t="n">
         <v>-17.95597773380875</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="5" t="n">
         <v>1.953016311667594</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="4" t="n">
         <v>45810</v>
       </c>
       <c r="B5" t="n">
         <v>-27</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="5" t="n">
         <v>-34.29412124019156</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="5" t="n">
         <v>-19.70587875980844</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="5" t="n">
         <v>3.721558813185679</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="4" t="n">
         <v>45817</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="5" t="n">
         <v>-25.72604067009718</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="5" t="n">
         <v>-29.45095126790861</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="5" t="n">
         <v>-22.00113007228575</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="5" t="n">
         <v>1.90049951284465</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="4" t="n">
         <v>45865</v>
       </c>
       <c r="B7" t="n">
         <v>-24</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="5" t="n">
         <v>-31.33351372056518</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="5" t="n">
         <v>-16.66648627943482</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="5" t="n">
         <v>3.741657386773942</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="4" t="n">
         <v>45908</v>
       </c>
       <c r="B8" t="n">
         <v>-12</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="5" t="n">
         <v>-16.2198942956584</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="5" t="n">
         <v>-7.780105704341597</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="5" t="n">
         <v>2.153046856444501</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="4" t="n">
         <v>45929</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="5" t="n">
         <v>-17.41956680034682</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="5" t="n">
         <v>-21.47991318826256</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="5" t="n">
         <v>-13.35922041243109</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="5" t="n">
         <v>2.07164336689002</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="4" t="n">
         <v>45999</v>
       </c>
       <c r="B10" t="n">
         <v>-13</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="5" t="n">
         <v>-17.22352685929889</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="5" t="n">
         <v>-8.776473140701114</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="5" t="n">
         <v>2.154900239297011</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="4" t="n">
         <v>46006</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="5" t="n">
         <v>-18.12622167916277</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="5" t="n">
         <v>-21.97416601886194</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="5" t="n">
         <v>-14.2782773394636</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="5" t="n">
         <v>1.963272983611567</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="4" t="n">
         <v>46048</v>
       </c>
       <c r="B12" t="n">
         <v>-27</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="5" t="n">
         <v>-34.34659760914891</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="5" t="n">
         <v>-19.65340239085109</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="5" t="n">
         <v>3.748332962798263</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="4" t="n">
         <v>46090</v>
       </c>
       <c r="B13" t="n">
         <v>-10</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="5" t="n">
         <v>-14.31690540079501</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="5" t="n">
         <v>-5.68309459920499</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="5" t="n">
         <v>2.202543227756331</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="4" t="n">
         <v>46104</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="5" t="n">
         <v>-14.58291589140467</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="5" t="n">
         <v>-18.6298217469324</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="5" t="n">
         <v>-10.53601003587695</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="5" t="n">
         <v>2.064785826397426</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="4" t="n">
         <v>46190</v>
       </c>
       <c r="B15" t="n">
         <v>-9</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="5" t="n">
         <v>-13.27070168398211</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="5" t="n">
         <v>-4.729298316017893</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="5" t="n">
         <v>2.178969469678452</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="4" t="n">
         <v>46197</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="5" t="n">
         <v>-14.53097719700153</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="5" t="n">
         <v>-18.51216464589934</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="5" t="n">
         <v>-10.54978974810371</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="5" t="n">
         <v>2.031255410967199</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="4" t="n">
         <v>46203</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="5" t="n">
         <v>-12.01437194316744</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="5" t="n">
         <v>-15.7839390373439</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="5" t="n">
         <v>-8.244804848990988</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="5" t="n">
         <v>1.923283858229192</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1687,79 +1747,123 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>observacoes_publicadas</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>primeira_data</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>ultima_data</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>numero_institutos</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>institutos</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>amostras_segmento_publicadas</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>fallbacks_amostra_segmento</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mulheres</t>
+          <t>Homens</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>16</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="4" t="n">
         <v>45684</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>46203</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Atlas, Ipec, PoderData</t>
         </is>
+      </c>
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Homens</t>
+          <t>Mulheres</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>16</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="4" t="n">
         <v>45684</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>46203</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>Atlas, Ipec, PoderData</t>
         </is>
       </c>
+      <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1770,16 +1874,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>descricao</t>
         </is>
@@ -1791,7 +1899,7 @@
           <t>Universo</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Brasil, abertura publicada de sexo.</t>
         </is>
@@ -1803,7 +1911,7 @@
           <t>Grupos</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Rótulos FEM/Feminino e MAS/Masculino são harmonizados como Mulheres e Homens.</t>
         </is>
@@ -1812,28 +1920,41 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Amostra e IC</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Usa amostra do segmento quando publicada; na ausência, o código aplica o fallback conservador já usado para aberturas.</t>
+          <t>Cobertura mínima</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Exige Mulheres e Homens com ao menos duas datas publicadas em cada grupo.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Amostra e faixa</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Usa amostra do segmento quando publicada; na ausência, aplica fallback conservador. A faixa é somente amostral e aproximada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Interpretação</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>As curvas são agregados de pesquisas disponíveis; não são previsão eleitoral.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>